--- a/Layout_Datos_Personales.xlsx
+++ b/Layout_Datos_Personales.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout_Personales" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Layout_Personales" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -54,7 +54,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -91,6 +91,18 @@
         <fgColor rgb="00ECF0F1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B4F72"/>
+        <bgColor rgb="001B4F72"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002980B9"/>
+        <bgColor rgb="002980B9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -118,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -148,6 +160,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -515,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -536,6 +560,10 @@
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -573,6 +601,11 @@
           <t>SALUD</t>
         </is>
       </c>
+      <c r="S3" s="11" t="inlineStr">
+        <is>
+          <t>ESCOLARIDAD Y ORIGEN</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
@@ -683,6 +716,30 @@
 Factor RH</t>
         </is>
       </c>
+      <c r="S4" s="13" t="inlineStr">
+        <is>
+          <t>GRADO_ESTUDIOS
+Clave Nivel Escolaridad</t>
+        </is>
+      </c>
+      <c r="T4" s="13" t="inlineStr">
+        <is>
+          <t>ESTADO_CIVIL
+Clave Estado Civil</t>
+        </is>
+      </c>
+      <c r="U4" s="13" t="inlineStr">
+        <is>
+          <t>ENTIDAD_NAC
+Clave Entidad Nacimiento</t>
+        </is>
+      </c>
+      <c r="V4" s="13" t="inlineStr">
+        <is>
+          <t>PAIS_NAC
+Clave País Nacimiento</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
@@ -773,6 +830,26 @@
       <c r="R5" s="8" t="inlineStr">
         <is>
           <t>Positivo/Negativo/NULL</t>
+        </is>
+      </c>
+      <c r="S5" s="8" t="inlineStr">
+        <is>
+          <t>Ej: 29</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>Ver hoja 'Estados Civiles'</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>Ej: 27</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
+          <t>Ej: 700</t>
         </is>
       </c>
     </row>
@@ -863,6 +940,20 @@
           <t>Positivo</t>
         </is>
       </c>
+      <c r="S6" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="T6" s="14" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="U6" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="V6" s="14" t="n">
+        <v>700</v>
+      </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="10" t="n">
@@ -953,6 +1044,20 @@
           <t>Positivo</t>
         </is>
       </c>
+      <c r="S7" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="T7" s="14" t="inlineStr">
+        <is>
+          <t>SO</t>
+        </is>
+      </c>
+      <c r="U7" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="V7" s="14" t="n">
+        <v>700</v>
+      </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="9" t="n">
@@ -1041,14 +1146,29 @@
           <t>Negativo</t>
         </is>
       </c>
+      <c r="S8" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="T8" s="14" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="U8" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="V8" s="14" t="n">
+        <v>700</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="A2:V2"/>
     <mergeCell ref="O3:P3"/>
+    <mergeCell ref="S3:V3"/>
     <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="A2:R2"/>
+    <mergeCell ref="A1:V1"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A1:R1"/>
     <mergeCell ref="D3:N3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
